--- a/e2e/expectedData/sub_Transfer.xlsx
+++ b/e2e/expectedData/sub_Transfer.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="66">
   <si>
     <t>DAFTAR PEMBAYARAN GAJI KARYAWAN</t>
   </si>
@@ -47,12 +47,135 @@
     <t>TOTAL TRANSFER (USD)</t>
   </si>
   <si>
+    <t>DIAN EVIYANTI APLUGI</t>
+  </si>
+  <si>
+    <t>Expat</t>
+  </si>
+  <si>
+    <t>Customer Care Manager (PJ)</t>
+  </si>
+  <si>
+    <t>$ 314.94</t>
+  </si>
+  <si>
+    <t>$ 0.00</t>
+  </si>
+  <si>
+    <t>AHMAD RIYANA SAPUTRA</t>
+  </si>
+  <si>
+    <t>Enterprise &amp; Wholesale Sales Solution Assistant Manager</t>
+  </si>
+  <si>
+    <t>$ 521.00</t>
+  </si>
+  <si>
+    <t>CLAUDIO DA COSTA ALVES</t>
+  </si>
+  <si>
+    <t>Outsource</t>
+  </si>
+  <si>
+    <t>Service Solution Support Officer</t>
+  </si>
+  <si>
+    <t>$ 219.26</t>
+  </si>
+  <si>
+    <t>CELIA MARIA REGO DE FATIMA</t>
+  </si>
+  <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>Human Capital Operational Assistant Manager</t>
+  </si>
+  <si>
+    <t>$ 455.00</t>
+  </si>
+  <si>
+    <t>FRIESCA AMELIA</t>
+  </si>
+  <si>
+    <t>Business Planning &amp; Performance Senior Manager</t>
+  </si>
+  <si>
+    <t>$ 701.00</t>
+  </si>
+  <si>
+    <t>RIMBUN SIBURIAN</t>
+  </si>
+  <si>
+    <t>Quality Assuance Senior Engineer</t>
+  </si>
+  <si>
+    <t>$ 1,189.08</t>
+  </si>
+  <si>
+    <t>Lestari Putri Cantika</t>
+  </si>
+  <si>
+    <t>Homestaff</t>
+  </si>
+  <si>
+    <t>Marketing &amp; Retail Senior Manager</t>
+  </si>
+  <si>
+    <t>$ 505.00</t>
+  </si>
+  <si>
+    <t>$ 45.00</t>
+  </si>
+  <si>
+    <t>$ 460.00</t>
+  </si>
+  <si>
+    <t>HERU YULIANTO</t>
+  </si>
+  <si>
+    <t>VP Marketing &amp; Sales</t>
+  </si>
+  <si>
+    <t>$ 4.35</t>
+  </si>
+  <si>
+    <t>$ 696.65</t>
+  </si>
+  <si>
+    <t>SYALDY KHARISMA ANANDA</t>
+  </si>
+  <si>
+    <t>O&amp;M Network Senior Manager</t>
+  </si>
+  <si>
+    <t>$ 383.59</t>
+  </si>
+  <si>
+    <t>$ 3.08</t>
+  </si>
+  <si>
+    <t>$ 380.52</t>
+  </si>
+  <si>
+    <t>AGOSTINHO GOMES FERNANDES</t>
+  </si>
+  <si>
+    <t>Customer Service Staff Ermera</t>
+  </si>
+  <si>
+    <t>$ 561.00</t>
+  </si>
+  <si>
+    <t>$ 1,750.00</t>
+  </si>
+  <si>
+    <t>$ -1,189.00</t>
+  </si>
+  <si>
     <t>ADROALDINO DA SILVA NORONHA TOME</t>
   </si>
   <si>
-    <t>Expat</t>
-  </si>
-  <si>
     <t>Customer Service Staff Manufahi</t>
   </si>
   <si>
@@ -65,163 +188,19 @@
     <t>$ 326.44</t>
   </si>
   <si>
-    <t>AGOSTINHO GOMES FERNANDES</t>
-  </si>
-  <si>
-    <t>Customer Service Staff Ermera</t>
-  </si>
-  <si>
-    <t>$ 561.00</t>
-  </si>
-  <si>
-    <t>$ 1,750.00</t>
-  </si>
-  <si>
-    <t>$ -1,189.00</t>
-  </si>
-  <si>
-    <t>CELIA MARIA REGO DE FATIMA</t>
-  </si>
-  <si>
-    <t>Human Capital Operational Assistant Manager</t>
-  </si>
-  <si>
-    <t>$ 455.00</t>
-  </si>
-  <si>
-    <t>$ 40.00</t>
-  </si>
-  <si>
-    <t>$ 415.00</t>
-  </si>
-  <si>
-    <t>CLAUDIO DA COSTA ALVES</t>
-  </si>
-  <si>
-    <t>Service Solution Support Officer</t>
-  </si>
-  <si>
-    <t>$ 219.26</t>
-  </si>
-  <si>
-    <t>$ 50.00</t>
-  </si>
-  <si>
-    <t>$ 169.26</t>
-  </si>
-  <si>
-    <t>DIAN EVIYANTI APLUGI</t>
-  </si>
-  <si>
-    <t>Customer Care Manager (PJ)</t>
-  </si>
-  <si>
-    <t>$ 314.94</t>
-  </si>
-  <si>
-    <t>$ 60.00</t>
-  </si>
-  <si>
-    <t>$ 254.94</t>
-  </si>
-  <si>
-    <t>AHMAD RIYANA SAPUTRA</t>
-  </si>
-  <si>
-    <t>Enterprise &amp; Wholesale Sales Solution Assistant Manager</t>
-  </si>
-  <si>
-    <t>$ 521.00</t>
-  </si>
-  <si>
-    <t>$ 70.00</t>
-  </si>
-  <si>
-    <t>$ 451.00</t>
-  </si>
-  <si>
-    <t>FRIESCA AMELIA</t>
-  </si>
-  <si>
-    <t>Business Planning &amp; Performance Senior Manager</t>
-  </si>
-  <si>
-    <t>$ 701.00</t>
-  </si>
-  <si>
-    <t>$ 0.00</t>
-  </si>
-  <si>
-    <t>HERU YULIANTO</t>
-  </si>
-  <si>
-    <t>Homestaff</t>
-  </si>
-  <si>
-    <t>VP Marketing &amp; Sales</t>
-  </si>
-  <si>
-    <t>$ 4.35</t>
-  </si>
-  <si>
-    <t>$ 696.65</t>
-  </si>
-  <si>
-    <t>RIMBUN SIBURIAN</t>
-  </si>
-  <si>
-    <t>Quality Assuance Senior Engineer</t>
-  </si>
-  <si>
-    <t>$ 1,038.11</t>
-  </si>
-  <si>
-    <t>$ -711.89</t>
-  </si>
-  <si>
-    <t>SYALDY KHARISMA ANANDA</t>
-  </si>
-  <si>
-    <t>O&amp;M Network Senior Manager</t>
-  </si>
-  <si>
-    <t>$ 383.59</t>
-  </si>
-  <si>
-    <t>$ 3.08</t>
-  </si>
-  <si>
-    <t>$ 380.52</t>
-  </si>
-  <si>
-    <t>Lestari Putri Cantika</t>
-  </si>
-  <si>
-    <t>Marketing &amp; Retail Senior Manager</t>
-  </si>
-  <si>
-    <t>$ 505.00</t>
-  </si>
-  <si>
-    <t>$ 45.00</t>
-  </si>
-  <si>
-    <t>$ 460.00</t>
-  </si>
-  <si>
     <t>TOTAL</t>
   </si>
   <si>
-    <t>$ 5,756.34</t>
-  </si>
-  <si>
-    <t>$ 3,802.43</t>
-  </si>
-  <si>
-    <t>$ 1,953.92</t>
-  </si>
-  <si>
-    <t>DILI, 26 August 2026</t>
+    <t>$ 5,907.31</t>
+  </si>
+  <si>
+    <t>$ 1,832.43</t>
+  </si>
+  <si>
+    <t>$ 4,074.89</t>
+  </si>
+  <si>
+    <t>DILI, 09 September 2026</t>
   </si>
   <si>
     <t>Human Resource</t>
@@ -695,7 +674,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="2">
-        <v>24016</v>
+        <v>79001</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>10</v>
@@ -713,7 +692,7 @@
         <v>14</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -721,25 +700,25 @@
         <v>2</v>
       </c>
       <c r="B6" s="2">
-        <v>26013</v>
+        <v>95008</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="G6" s="2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -747,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="B7" s="2">
-        <v>92003</v>
+        <v>24005</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="G7" s="2" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -773,25 +752,25 @@
         <v>4</v>
       </c>
       <c r="B8" s="2">
-        <v>24005</v>
+        <v>92003</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -799,25 +778,25 @@
         <v>5</v>
       </c>
       <c r="B9" s="2">
-        <v>79001</v>
+        <v>91009</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -825,25 +804,25 @@
         <v>6</v>
       </c>
       <c r="B10" s="2">
-        <v>95008</v>
+        <v>81010</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -851,25 +830,25 @@
         <v>7</v>
       </c>
       <c r="B11" s="2">
-        <v>91009</v>
+        <v>999999</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -880,22 +859,22 @@
         <v>74003</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -903,25 +882,25 @@
         <v>9</v>
       </c>
       <c r="B13" s="2">
-        <v>81010</v>
+        <v>91015</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -929,25 +908,25 @@
         <v>10</v>
       </c>
       <c r="B14" s="2">
-        <v>91015</v>
+        <v>26013</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -955,43 +934,43 @@
         <v>11</v>
       </c>
       <c r="B15" s="2">
-        <v>999999</v>
+        <v>24016</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="4" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="3" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -999,18 +978,18 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E19"/>
       <c r="F19" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:8" customHeight="1" ht="37.5">
@@ -1020,20 +999,20 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E21"/>
       <c r="F21" s="1" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E22"/>
       <c r="F22" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/e2e/expectedData/sub_Transfer.xlsx
+++ b/e2e/expectedData/sub_Transfer.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="75">
   <si>
     <t>DAFTAR PEMBAYARAN GAJI KARYAWAN</t>
   </si>
@@ -47,19 +47,145 @@
     <t>TOTAL TRANSFER (USD)</t>
   </si>
   <si>
+    <t>FRIESCA AMELIA</t>
+  </si>
+  <si>
+    <t>Expat</t>
+  </si>
+  <si>
+    <t>Business Planning &amp; Performance Senior Manager</t>
+  </si>
+  <si>
+    <t>$ 701.00</t>
+  </si>
+  <si>
+    <t>$ 0.00</t>
+  </si>
+  <si>
+    <t>Lestari Putri Cantika</t>
+  </si>
+  <si>
+    <t>Homestaff</t>
+  </si>
+  <si>
+    <t>Marketing &amp; Retail Senior Manager</t>
+  </si>
+  <si>
+    <t>$ 505.00</t>
+  </si>
+  <si>
+    <t>$ 45.00</t>
+  </si>
+  <si>
+    <t>$ 460.00</t>
+  </si>
+  <si>
+    <t>HERU YULIANTO</t>
+  </si>
+  <si>
+    <t>VP Marketing &amp; Sales</t>
+  </si>
+  <si>
+    <t>$ 4.35</t>
+  </si>
+  <si>
+    <t>$ 696.65</t>
+  </si>
+  <si>
+    <t>SYALDY KHARISMA ANANDA</t>
+  </si>
+  <si>
+    <t>O&amp;M Network Senior Manager</t>
+  </si>
+  <si>
+    <t>$ 383.59</t>
+  </si>
+  <si>
+    <t>$ 3.08</t>
+  </si>
+  <si>
+    <t>$ 380.52</t>
+  </si>
+  <si>
+    <t>AGOSTINHO GOMES FERNANDES</t>
+  </si>
+  <si>
+    <t>Customer Service Staff Ermera</t>
+  </si>
+  <si>
+    <t>$ 561.00</t>
+  </si>
+  <si>
+    <t>$ 1,750.00</t>
+  </si>
+  <si>
+    <t>$ -1,189.00</t>
+  </si>
+  <si>
+    <t>ADROALDINO DA SILVA NORONHA TOME</t>
+  </si>
+  <si>
+    <t>Outsource</t>
+  </si>
+  <si>
+    <t>Customer Service Staff Manufahi</t>
+  </si>
+  <si>
+    <t>$ 356.44</t>
+  </si>
+  <si>
+    <t>$ 37.20</t>
+  </si>
+  <si>
+    <t>$ 319.24</t>
+  </si>
+  <si>
+    <t>CELIA MARIA REGO DE FATIMA</t>
+  </si>
+  <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>Human Capital Operational Assistant Manager</t>
+  </si>
+  <si>
+    <t>$ 455.00</t>
+  </si>
+  <si>
+    <t>$ 53.60</t>
+  </si>
+  <si>
+    <t>$ 401.40</t>
+  </si>
+  <si>
+    <t>CLAUDIO DA COSTA ALVES</t>
+  </si>
+  <si>
+    <t>Service Solution Support Officer</t>
+  </si>
+  <si>
+    <t>$ 219.26</t>
+  </si>
+  <si>
+    <t>$ 58.40</t>
+  </si>
+  <si>
+    <t>$ 160.86</t>
+  </si>
+  <si>
     <t>DIAN EVIYANTI APLUGI</t>
   </si>
   <si>
-    <t>Expat</t>
-  </si>
-  <si>
     <t>Customer Care Manager (PJ)</t>
   </si>
   <si>
     <t>$ 314.94</t>
   </si>
   <si>
-    <t>$ 0.00</t>
+    <t>$ 72.00</t>
+  </si>
+  <si>
+    <t>$ 242.94</t>
   </si>
   <si>
     <t>AHMAD RIYANA SAPUTRA</t>
@@ -71,37 +197,10 @@
     <t>$ 521.00</t>
   </si>
   <si>
-    <t>CLAUDIO DA COSTA ALVES</t>
-  </si>
-  <si>
-    <t>Outsource</t>
-  </si>
-  <si>
-    <t>Service Solution Support Officer</t>
-  </si>
-  <si>
-    <t>$ 219.26</t>
-  </si>
-  <si>
-    <t>CELIA MARIA REGO DE FATIMA</t>
-  </si>
-  <si>
-    <t>Local</t>
-  </si>
-  <si>
-    <t>Human Capital Operational Assistant Manager</t>
-  </si>
-  <si>
-    <t>$ 455.00</t>
-  </si>
-  <si>
-    <t>FRIESCA AMELIA</t>
-  </si>
-  <si>
-    <t>Business Planning &amp; Performance Senior Manager</t>
-  </si>
-  <si>
-    <t>$ 701.00</t>
+    <t>$ 90.80</t>
+  </si>
+  <si>
+    <t>$ 430.20</t>
   </si>
   <si>
     <t>RIMBUN SIBURIAN</t>
@@ -113,79 +212,7 @@
     <t>$ 1,189.08</t>
   </si>
   <si>
-    <t>Lestari Putri Cantika</t>
-  </si>
-  <si>
-    <t>Homestaff</t>
-  </si>
-  <si>
-    <t>Marketing &amp; Retail Senior Manager</t>
-  </si>
-  <si>
-    <t>$ 505.00</t>
-  </si>
-  <si>
-    <t>$ 45.00</t>
-  </si>
-  <si>
-    <t>$ 460.00</t>
-  </si>
-  <si>
-    <t>HERU YULIANTO</t>
-  </si>
-  <si>
-    <t>VP Marketing &amp; Sales</t>
-  </si>
-  <si>
-    <t>$ 4.35</t>
-  </si>
-  <si>
-    <t>$ 696.65</t>
-  </si>
-  <si>
-    <t>SYALDY KHARISMA ANANDA</t>
-  </si>
-  <si>
-    <t>O&amp;M Network Senior Manager</t>
-  </si>
-  <si>
-    <t>$ 383.59</t>
-  </si>
-  <si>
-    <t>$ 3.08</t>
-  </si>
-  <si>
-    <t>$ 380.52</t>
-  </si>
-  <si>
-    <t>AGOSTINHO GOMES FERNANDES</t>
-  </si>
-  <si>
-    <t>Customer Service Staff Ermera</t>
-  </si>
-  <si>
-    <t>$ 561.00</t>
-  </si>
-  <si>
-    <t>$ 1,750.00</t>
-  </si>
-  <si>
-    <t>$ -1,189.00</t>
-  </si>
-  <si>
-    <t>ADROALDINO DA SILVA NORONHA TOME</t>
-  </si>
-  <si>
-    <t>Customer Service Staff Manufahi</t>
-  </si>
-  <si>
-    <t>$ 356.44</t>
-  </si>
-  <si>
-    <t>$ 30.00</t>
-  </si>
-  <si>
-    <t>$ 326.44</t>
+    <t>$ -560.92</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -194,13 +221,13 @@
     <t>$ 5,907.31</t>
   </si>
   <si>
-    <t>$ 1,832.43</t>
-  </si>
-  <si>
-    <t>$ 4,074.89</t>
-  </si>
-  <si>
-    <t>DILI, 09 September 2026</t>
+    <t>$ 3,864.43</t>
+  </si>
+  <si>
+    <t>$ 2,042.89</t>
+  </si>
+  <si>
+    <t>DILI, 10 September 2026</t>
   </si>
   <si>
     <t>Human Resource</t>
@@ -674,7 +701,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="2">
-        <v>79001</v>
+        <v>91009</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>10</v>
@@ -700,25 +727,25 @@
         <v>2</v>
       </c>
       <c r="B6" s="2">
-        <v>95008</v>
+        <v>999999</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -726,25 +753,25 @@
         <v>3</v>
       </c>
       <c r="B7" s="2">
-        <v>24005</v>
+        <v>74003</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -752,25 +779,25 @@
         <v>4</v>
       </c>
       <c r="B8" s="2">
-        <v>92003</v>
+        <v>91015</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -778,25 +805,25 @@
         <v>5</v>
       </c>
       <c r="B9" s="2">
-        <v>91009</v>
+        <v>26013</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -804,25 +831,25 @@
         <v>6</v>
       </c>
       <c r="B10" s="2">
-        <v>81010</v>
+        <v>24016</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -830,25 +857,25 @@
         <v>7</v>
       </c>
       <c r="B11" s="2">
-        <v>999999</v>
+        <v>92003</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -856,25 +883,25 @@
         <v>8</v>
       </c>
       <c r="B12" s="2">
-        <v>74003</v>
+        <v>24005</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -882,25 +909,25 @@
         <v>9</v>
       </c>
       <c r="B13" s="2">
-        <v>91015</v>
+        <v>79001</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -908,25 +935,25 @@
         <v>10</v>
       </c>
       <c r="B14" s="2">
-        <v>26013</v>
+        <v>95008</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -934,43 +961,43 @@
         <v>11</v>
       </c>
       <c r="B15" s="2">
-        <v>24016</v>
+        <v>81010</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="4" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="3" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -978,18 +1005,18 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="E18"/>
       <c r="F18"/>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="E19"/>
       <c r="F19" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:8" customHeight="1" ht="37.5">
@@ -999,20 +1026,20 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="E21"/>
       <c r="F21" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E22"/>
       <c r="F22" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
